--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>136439708</v>
       </c>
       <c r="B14" t="n">
-        <v>101572</v>
+        <v>101575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>136439708</v>
       </c>
       <c r="B14" t="n">
-        <v>101575</v>
+        <v>101576</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2230,7 +2230,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Maria Magnusson, Emilia Fagerberg</t>
+          <t>Emilia Fagerberg, Maria Magnusson, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>136439708</v>
       </c>
       <c r="B14" t="n">
-        <v>101576</v>
+        <v>101581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emilia Fagerberg, Maria Magnusson, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Maria Magnusson, Emilia Fagerberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>136439708</v>
       </c>
       <c r="B14" t="n">
-        <v>101581</v>
+        <v>101583</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2230,7 +2230,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emilia Fagerberg, Maria Magnusson, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Maria Magnusson, Emilia Fagerberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>136439708</v>
       </c>
       <c r="B14" t="n">
-        <v>101583</v>
+        <v>101589</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>136439708</v>
       </c>
       <c r="B14" t="n">
-        <v>101589</v>
+        <v>101591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>136439708</v>
       </c>
       <c r="B14" t="n">
-        <v>101591</v>
+        <v>101592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2126,10 +2126,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136439708</v>
+        <v>135698631</v>
       </c>
       <c r="B14" t="n">
-        <v>101592</v>
+        <v>101645</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,27 +2156,30 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hammaren, Vg</t>
+          <t>Vägkant SÖ om Hammaren, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>429615</v>
+        <v>429617</v>
       </c>
       <c r="R14" t="n">
-        <v>6425458</v>
+        <v>6425456</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2200,17 +2203,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Östra sidan i bankslänt.</t>
+          <t>I vögskärningen nedanför en ung ek</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,26 +2222,143 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135698631</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136439708</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101592</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222886</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hammaren, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>429615</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6425458</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Östra sidan i bankslänt.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Elvira Ljungberg</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Emilia Fagerberg, Maria Magnusson, Elvira Ljungberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136439708</t>
         </is>
@@ -2259,6 +2379,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>135698631</v>
       </c>
       <c r="B14" t="n">
-        <v>101645</v>
+        <v>101648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>135698631</v>
       </c>
       <c r="B14" t="n">
-        <v>101648</v>
+        <v>101654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>135698631</v>
       </c>
       <c r="B14" t="n">
-        <v>101654</v>
+        <v>101666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>135698631</v>
       </c>
       <c r="B14" t="n">
-        <v>101666</v>
+        <v>101667</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>135698631</v>
       </c>
       <c r="B14" t="n">
-        <v>101667</v>
+        <v>101670</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16467-2025 artfynd.xlsx
+++ b/artfynd/A 16467-2025 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>135698631</v>
       </c>
       <c r="B14" t="n">
-        <v>101670</v>
+        <v>101674</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
